--- a/output/pdf_financials_xlsx/SBTC.xlsx
+++ b/output/pdf_financials_xlsx/SBTC.xlsx
@@ -1091,16 +1091,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.645351</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.250985</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.038749</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.011891</v>
       </c>
     </row>
     <row r="35">
@@ -1129,16 +1129,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.645351</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.250985</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.038749</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.011891</v>
       </c>
     </row>
     <row r="37">
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.949574</v>
+        <v>0.304223</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.254779</v>
+        <v>1.003794</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.758109</v>
+        <v>0.71936</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.465439</v>
+        <v>0.453548</v>
       </c>
     </row>
     <row r="49">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/SBTC.xlsx
+++ b/output/pdf_financials_xlsx/SBTC.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.162327</v>
+        <v>0.338662</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.207922</v>
+        <v>0.463489</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.039535</v>
+        <v>0.164023</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.021313</v>
+        <v>0.080153</v>
       </c>
     </row>
     <row r="8">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.162327</v>
+        <v>0.338662</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.207922</v>
+        <v>0.463489</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.039535</v>
+        <v>0.164023</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.021313</v>
+        <v>0.080153</v>
       </c>
     </row>
     <row r="11">
@@ -2634,13 +2634,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.091793</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.254793</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.030435</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -4048,7 +4048,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.091793</v>
       </c>
@@ -4760,7 +4764,11 @@
           <t>Management &amp; directors fees 9</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>0.176335</v>
       </c>
